--- a/docs/research/provinces/SportsHub-Manitoba.xlsx
+++ b/docs/research/provinces/SportsHub-Manitoba.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,27 +559,21 @@
           <t>Altona</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>https://altonabasketball.com/</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Community youth basketball; fields tournament teams ($50/team entry incl. association T-shirt and Basketball Manitoba-provided injury insurance)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>reported</t>
@@ -615,14 +611,11 @@
           <t>Beausejour (Sunrise School Division area, exact town unconfirmed)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>mhovorka@sunrisesd.ca</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Mary-Jo Hovorka — listed contact (role not stated)</t>
@@ -633,13 +626,11 @@
           <t>Boys basketball, ages 14-17 (per directory listing)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>community program (possibly school-community hybrid — contact uses Sunrise School Division email)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -707,13 +698,11 @@
           <t>Fall Bobcat Basketball Academy for Grades 5-8 (historically K-12); annual summer basketball camps; free annual Holiday Hoops youth camp (Grades 3/4-12) at the Healthy Living Centre</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>university-affiliated youth academy/camps (not school-board varsity)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>verified</t>
@@ -781,13 +770,11 @@
           <t>Girls 14U, 16U, 17U club teams; tryouts at Henry Champ and HLC South</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>university-affiliated youth program</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>reported</t>
@@ -865,7 +852,6 @@
           <t>university-affiliated club program</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>verified</t>
@@ -876,7 +862,6 @@
           <t>http://www.gobobcats.ca/juniorbobcats</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -939,7 +924,6 @@
           <t>university-affiliated youth club/academy</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>verified</t>
@@ -977,7 +961,6 @@
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>204-720-7778</t>
@@ -988,7 +971,6 @@
           <t>treedell33@icloud.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Wardell Smith — club contact (PSO registry)</t>
@@ -999,13 +981,11 @@
           <t>Boys team age 13</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1016,7 +996,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1039,7 +1018,6 @@
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>204-901-0360</t>
@@ -1117,7 +1095,6 @@
           <t>Dauphin</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>204-572-4484</t>
@@ -1143,13 +1120,11 @@
           <t>Club teams: 14U girls, 15U boys, 18U boys (Dauphin + Grandview); hosted club basketball tournament May 2022 for boys &amp; girls teams ages 14-18 ($350/team, 3-game guarantee)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>community club (volunteer-run; contacts use Mountain View School Division emails, but operates as a club, not a school team)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1187,7 +1162,6 @@
           <t>Morden</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>204-822-5431</t>
@@ -1203,19 +1177,16 @@
           <t>https://morden.ca/recreation-organizations</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Municipal youth recreational basketball programming (youth rec basketball; 12+ basketball) offered through City of Morden recreation</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>municipal recreation program (no dedicated club found in Morden)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1268,14 +1239,11 @@
           <t>recreation@whereyoubelong.ca</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Boys club teams born 2010-2013; coach with Los Angeles background; venue Niverville Recreation Centre</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -1425,19 +1393,16 @@
           <t>https://nivervillerec.ca/programs/</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Weekly instructional youth basketball ages 6–9 and 9–14 at the CRRC; hosts Jr. NBA Youth Basketball Camp (ages 5–12)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>town recreation program (multi-sport org)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1480,14 +1445,11 @@
           <t>Niverville Community Resource &amp; Recreation Centre, Niverville, MB (program venue)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Community youth basketball for boys and girls ages 4-18, delivered in Niverville under the Winnipeg Minor Basketball Association's community programming at the Niverville CRRC</t>
@@ -1545,7 +1507,6 @@
           <t>Niverville area (Eastman/Central region)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>204-998-4462</t>
@@ -1581,7 +1542,6 @@
           <t>community nonprofit / league operator with select teams</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1592,7 +1552,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1615,7 +1574,6 @@
           <t>Portage la Prairie</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>204-870-1071</t>
@@ -1626,7 +1584,6 @@
           <t>centralplainsbasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Darin Arnold — club contact (PSO registry)</t>
@@ -1647,7 +1604,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1658,7 +1614,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1681,14 +1636,11 @@
           <t>Selkirk</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Blake Hamm — club contact (PSO registry)</t>
@@ -1709,7 +1661,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1720,7 +1671,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1748,7 +1698,6 @@
           <t>Lord Selkirk Regional Comprehensive Secondary School, 221 Mercy Street, Selkirk, MB (program base)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
@@ -1779,7 +1728,6 @@
           <t>community nonprofit (feeder club aligned with Lord Selkirk Regional 'Royals' school program but operated as a Basketball Manitoba member club)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1817,8 +1765,6 @@
           <t>Southern Manitoba (Winkler/Morden area)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>stephen@bigcountrybasketball.com</t>
@@ -1839,13 +1785,11 @@
           <t>Girls club program ages 12-17 plus basketball-specific training &amp; development for all levels (LTAD-based holistic model)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>private club/training program</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1856,7 +1800,6 @@
           <t>https://www.bigcountrybasketball.com/about</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1879,7 +1822,6 @@
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>204-998-4462</t>
@@ -1957,7 +1899,6 @@
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>204-998-4462</t>
@@ -2035,8 +1976,6 @@
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>jdykerman@hsd.ca</t>
@@ -2109,7 +2048,6 @@
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>204-370-6507</t>
@@ -2187,7 +2125,6 @@
           <t>The Pas</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>204-620-6110</t>
@@ -2213,13 +2150,11 @@
           <t>Youth basketball association programming for The Pas &amp; area (northern Manitoba)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2257,9 +2192,6 @@
           <t>Thompson</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>https://www.instagram.com/juniorbisons/</t>
@@ -2275,13 +2207,11 @@
           <t>Club basketball program based in Thompson; girls club ages 13-17 listed; Junior Bison Thompson athletes received member pricing at Prairie Elite Academy camps held at Wapanohk Community School (Grades 5-12)</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2359,7 +2289,6 @@
           <t>private academy/training + club</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2370,7 +2299,6 @@
           <t>https://btbdhoopsxrelentless.ca/</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2393,8 +2321,6 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>prairieelitebasketballacademy@gmail.com</t>
@@ -2415,13 +2341,11 @@
           <t>Female-focused training academy: development camps for girls Grades 7-12 and players camps for boys &amp; girls ages 11-18 held in Winkler (2018); ran 'Prairie Elite South' club team tryouts in Winkler for girls born 2002+ (2019)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -2459,8 +2383,6 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>winklerbasketballclub@gmail.com</t>
@@ -2533,8 +2455,6 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>winklerminorbasketball@gmail.com</t>
@@ -2545,7 +2465,6 @@
           <t>https://winklerminorbasketball.weebly.com/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Spring house league (begins March) for Winkler &amp; area, boys and girls divisions Grades 3&amp;4, 5&amp;6, 7&amp;8; registration $75; mission: promote basketball skill development in young athletes in the Winkler area</t>
@@ -2603,8 +2522,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>204elite@gmail.com</t>
@@ -2635,7 +2552,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2673,14 +2589,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>ambush.club.basketball@gmail.com</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Jaira Labelle — club contact (PSO registry)</t>
@@ -2701,7 +2614,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2712,7 +2624,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2735,8 +2646,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>atlasbball@gmail.com</t>
@@ -2767,7 +2676,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2778,7 +2686,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2801,7 +2708,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>431-999-7269</t>
@@ -2837,7 +2743,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2875,14 +2780,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>attacksouthbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Tara Kelly, Erin Sheldon, Ogo Okwumabua — club contacts (PSO registry)</t>
@@ -2945,17 +2847,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Boys 18U club team; tryouts at Sturgeon Heights Community Centre</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>community club</t>
@@ -2976,7 +2872,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2024-07-17T00:00:00-05:00&amp;max-results=50</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2999,15 +2894,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>info@chiefsbball.club</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Indigenous-focused club in partnership with Interlake Reserve Tribal Council (IRTC); boys &amp; girls born 2011-2013 (earlier U12); low-cost $10 tryouts at Université de Saint-Boniface; IRTC Chiefs also field U21 travel teams for Alberta Indigenous Games</t>
@@ -3023,7 +2914,6 @@
           <t>community nonprofit (Indigenous partnership)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3143,7 +3033,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>204-500-9033</t>
@@ -3221,7 +3110,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>431-334-5169</t>
@@ -3232,7 +3120,6 @@
           <t>delitembb@gmail.com</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Anton Dziuba — club contact (PSO registry)</t>
@@ -3268,7 +3155,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3373,14 +3259,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>downtowndawgs@outlook.com</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Jordan Fotheringham — club contact (PSO registry)</t>
@@ -3401,7 +3284,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3412,7 +3294,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3435,15 +3316,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>dynastywpg@gmail.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Girls rep teams, born 2009–2012; tryouts at Sport Manitoba (145 Pacific Ave)</t>
@@ -3506,14 +3383,11 @@
           <t>145 Pacific Avenue, Winnipeg, Manitoba R3B 2Z6</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>empireelitehoops@gmail.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Boys teams born 2008–2014, girls born 2010–2012; trains at BATTLE 204 facility; local, national and USA tournaments; tryouts at Sport for Life Centre and YFC Winnipeg</t>
@@ -3529,7 +3403,6 @@
           <t>community club (nonprofit status unverified)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3622,7 +3495,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3809,8 +3681,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>ignitebasketballwinnipeg@gmail.com</t>
@@ -3883,27 +3753,21 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>junioralliancebasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Boys born 2008-2014 and girls born 2009 club teams; tryouts at Red River College Polytech South Gym</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3914,7 +3778,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2025-07-02T00:00:00-05:00&amp;max-results=50</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3937,8 +3800,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>juniorbisonboysbasketball@gmail.com</t>
@@ -3949,13 +3810,11 @@
           <t>https://www.juniorbisonboys.ca/</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>Youth basketball club offering programming to boys ages 12-17</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>community club</t>
@@ -4187,7 +4046,6 @@
           <t>https://www.kirkfieldwestwood.com/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>WMBA founding community centre (1997); WMBA Foundation outdoor courts on site; fields WMBA catchment teams</t>
@@ -4245,8 +4103,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>mkraus.legacyprep@gmail.com</t>
@@ -4339,7 +4195,6 @@
           <t>https://lindenwoodscc.com/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>WMBA founding community centre (1997); current WMBA indoor court venue; hosts club tryouts (World Class Hoopers, Ignite, Triumph)</t>
@@ -4397,7 +4252,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>204-292-3018</t>
@@ -4433,7 +4287,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4471,7 +4324,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>204-292-3018</t>
@@ -4507,7 +4359,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4627,27 +4478,21 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>bballmastery@gmail.com</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Boys &amp; girls club teams born 2009; Instagram @masterybasketball</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>reported</t>
@@ -4658,7 +4503,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2023-12-14T00:00:00-06:00&amp;max-results=50</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4681,8 +4525,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>info@northstarbasketball.ca</t>
@@ -4713,7 +4555,6 @@
           <t>private academy operated by nonprofit foundation</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>verified</t>
@@ -4771,7 +4612,6 @@
           <t>https://oxfordheights.pointstreaksites.com/view/oxfordheights/sports-1/basketball-4</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Transcona-area catchment for WMBA basketball; outdoor court (built 2014) hosts WMBA x ELEVATE 3x3 summer league</t>
@@ -4829,7 +4669,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>204-294-7931</t>
@@ -4880,7 +4719,6 @@
           <t>https://www.basketballmanitoba.ca/2024/08/pba-winnipeg-announces-2024-25.html</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4985,11 +4823,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Boys rep (17U entry in fall league); U18 team referenced in coach bios</t>
@@ -5005,7 +4838,6 @@
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5043,7 +4875,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>204-995-1682</t>
@@ -5094,7 +4925,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5117,7 +4947,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>204-891-0144</t>
@@ -5153,7 +4982,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5164,7 +4992,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5187,7 +5014,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>204-951-2070</t>
@@ -5198,7 +5024,6 @@
           <t>wpgrisingstarclub@gmail.com</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Jarred Suyat, Diowe Bacanto, Jerrold Suyat — club contacts (PSO registry)</t>
@@ -5219,7 +5044,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5339,7 +5163,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>204-299-7918</t>
@@ -5350,7 +5173,6 @@
           <t>wgpsummitbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Tara Meneer — club contact (PSO registry)</t>
@@ -5371,7 +5193,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5382,7 +5203,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5405,15 +5225,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>jbourcier28@gmail.com</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Boys rep team (2008 birth year); tryouts at Sturgeon Heights Community Centre</t>
@@ -5429,7 +5245,6 @@
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5440,7 +5255,6 @@
           <t>https://www.basketballmanitoba.ca/2025/08/showtime-basketball-club-announces.html</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5483,7 +5297,6 @@
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
@@ -5561,7 +5374,6 @@
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>WMBA catchment basketball ages 7-17 (7-8 co-ed; 9-12 girls / 9-13 boys; 13-17 girls / 14-17 boys) across Richmond and Waverley sites</t>
@@ -5592,7 +5404,6 @@
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5615,27 +5426,21 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>wpgwildcatsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Girls club teams ages 13-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>community club (girls-focused)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5646,7 +5451,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2023-12-14T00:00:00-06:00&amp;max-results=50</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5669,7 +5473,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>204-914-5663</t>
@@ -5720,7 +5523,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5743,7 +5545,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>204-333-7005</t>
@@ -5754,7 +5555,6 @@
           <t>unitebasketball22@gmail.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Jordan Lopez — club contact (PSO registry)</t>
@@ -5765,13 +5565,11 @@
           <t>Boys &amp; girls rep teams ages 11–12 and 15–16</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5814,26 +5612,21 @@
           <t>323 - 145 Pacific Avenue, Winnipeg, Manitoba</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>info@pegcityball.ca</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Boys club teams born 2008-2010 (2024-25 tryout announcement)</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5871,11 +5664,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Boys teams 2009–2011 births and 2011 girls team</t>
@@ -5891,7 +5679,6 @@
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6011,7 +5798,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>204-471-1111</t>
@@ -6027,7 +5813,6 @@
           <t>https://visioneliteacademy.org/basketball</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>Multi-city private academy (Calgary HQ; Winnipeg, Edmonton, Fraser Valley): Vision Academy ages 7-11, Premier League ages 12-17 (internal seasonal league), Vision Basketball Club ages 12-18 competitive; 10-week year-round sessions; pay-per-session options</t>
@@ -6085,14 +5870,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>bballwestside@gmail.com</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Clarence Vigilance, Coach</t>
@@ -6103,13 +5885,11 @@
           <t>Boys club teams born 2013-2014; tryouts at Sport Manitoba (145 Pacific Ave)</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6167,7 +5947,6 @@
           <t>https://whyteridge.ca/sports/basketball/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>House-league basketball via WMBA catchment: ages 7-8 co-ed 3v3, 9-12 (+13 boys), 14-17 (+13 girls) 5v5; fees WMBA $179 + CC $80 + $9 Canada Basketball</t>
@@ -6394,7 +6173,6 @@
           <t>Bronx Park Community Centre, 720 Henderson Hwy (home facility)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>winnipegblizzards@gmail.com</t>
@@ -6467,8 +6245,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>chaoswinnipeg@gmail.com</t>
@@ -6489,7 +6265,6 @@
           <t>Girls competitive club teams (15U-17U, born 2009-2012); summer/winter skills clinics boys 7-11 and girls 6-18; own outdoor practice courts; travels to national tournaments (BBall Nationals 2025)</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>community club (girls-focused)</t>
@@ -6537,15 +6312,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>jq14@shaw.ca</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>Boys rep team (2010 birth year); tryouts at Sturgeon Heights Community Centre (210 Rita St.)</t>
@@ -6561,7 +6332,6 @@
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6572,7 +6342,6 @@
           <t>https://www.basketballmanitoba.ca/2025/08/winnipeg-cobras-basketball-club-hosting.html</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6600,7 +6369,6 @@
           <t>Duckworth Centre, University of Winnipeg, Winnipeg, MB</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>al.cox@uwinnipeg.ca</t>
@@ -6631,7 +6399,6 @@
           <t>university-affiliated club program</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6674,7 +6441,6 @@
           <t>Duckworth Centre, 400 Spence St, Winnipeg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>jrwesmen@gmail.com</t>
@@ -6705,7 +6471,6 @@
           <t>university-affiliated youth program (girls)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6798,7 +6563,6 @@
           <t>https://www.wmba.ca/</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6821,27 +6585,21 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>wpgsaints@gmail.com</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Boys club team born 2010; tryouts at Valour Community Centre (715 Telfer St N)</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6852,7 +6610,6 @@
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?max-results=100</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6915,7 +6672,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6926,7 +6682,6 @@
           <t>https://www.winnipegteammayhem.com/en/</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6949,8 +6704,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>winnipegwolves@gmail.com</t>
@@ -6971,7 +6724,6 @@
           <t>Operating since 2006; recent seasons girls U15/U18 teams; training programs; tryouts at Université de Saint-Boniface</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>community club</t>
@@ -7019,11 +6771,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>Boys team (2010 birth year)</t>
@@ -7039,7 +6786,6 @@
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7077,8 +6823,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>worldclasshoopers@gmail.com</t>
@@ -7109,7 +6853,6 @@
           <t>community club (nonprofit status unverified)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7177,13 +6920,11 @@
           <t>Free boys club basketball ages 13-17 (grades 8-12), Thursdays Sep-Dec: skills, scrimmages, faith-based mentorship; first-year program forming new teams weekly</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>multi-sport/faith-based charity youth org</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7194,7 +6935,6 @@
           <t>https://yfc.ca/winnipeg/program/club-basketball/</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7247,13 +6987,11 @@
           <t>Free weekly boys basketball (ages 13–17, Grades 8–12), Thursdays Sept–Dec; skills + scrimmages; facility also hosts club tryouts (e.g., Empire)</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>faith-based charity / multi-sport youth org (registered charity #119307619 RR0001)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11196,7 +10934,6 @@
           <t>Beausejour (Sunrise School Division area, exact town unconfirmed)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>mhovorka@sunrisesd.ca</t>
@@ -11207,7 +10944,6 @@
           <t>Mary-Jo Hovorka — listed contact (role not stated)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11363,7 +11099,6 @@
           <t>Wardell Smith — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11450,7 +11185,6 @@
           <t>recreation@mymorden.ca</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>https://morden.ca/recreation-organizations</t>
@@ -11478,8 +11212,6 @@
           <t>recreation@whereyoubelong.ca</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11534,7 +11266,6 @@
           <t>recreation@whereyoubelong.ca</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>https://nivervillerec.ca/programs/</t>
@@ -11599,7 +11330,6 @@
           <t>Darin Arnold — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11612,7 +11342,6 @@
           <t>Selkirk</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
@@ -11623,7 +11352,6 @@
           <t>Blake Hamm — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11636,7 +11364,6 @@
           <t>Selkirk</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
@@ -11664,7 +11391,6 @@
           <t>Southern Manitoba (Winkler/Morden area)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>stephen@bigcountrybasketball.com</t>
@@ -11756,7 +11482,6 @@
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>jdykerman@hsd.ca</t>
@@ -11848,8 +11573,6 @@
           <t>Thompson</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Kristin Donovan — listed contact for Thompson girls club (ages 13-17) in the NBA/eCrew 'Find a Place to Play' Manitoba directory</t>
@@ -11904,7 +11627,6 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>prairieelitebasketballacademy@gmail.com</t>
@@ -11932,7 +11654,6 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>winklerbasketballclub@gmail.com</t>
@@ -11960,13 +11681,11 @@
           <t>Winkler</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>winklerminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>https://winklerminorbasketball.weebly.com/</t>
@@ -11984,7 +11703,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>204elite@gmail.com</t>
@@ -12012,7 +11730,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>ambush.club.basketball@gmail.com</t>
@@ -12023,7 +11740,6 @@
           <t>Jaira Labelle — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12036,7 +11752,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>atlasbball@gmail.com</t>
@@ -12096,7 +11811,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>attacksouthbasketball@gmail.com</t>
@@ -12107,7 +11821,6 @@
           <t>Tara Kelly, Erin Sheldon, Ogo Okwumabua — club contacts (PSO registry)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12120,14 +11833,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>info@chiefsbball.club</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12219,7 +11929,6 @@
           <t>Anton Dziuba — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12264,7 +11973,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>downtowndawgs@outlook.com</t>
@@ -12275,7 +11983,6 @@
           <t>Jordan Fotheringham — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12288,14 +11995,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>dynastywpg@gmail.com</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12308,14 +12012,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>empireelitehoops@gmail.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12424,7 +12125,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>ignitebasketballwinnipeg@gmail.com</t>
@@ -12452,14 +12152,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>junioralliancebasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12472,13 +12169,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>juniorbisonboysbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>https://www.juniorbisonboys.ca/</t>
@@ -12570,7 +12265,6 @@
           <t>office@kwcc.net</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>https://www.kirkfieldwestwood.com/</t>
@@ -12588,7 +12282,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>mkraus.legacyprep@gmail.com</t>
@@ -12626,7 +12319,6 @@
           <t>manager@lindenwoodscc.com</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>https://lindenwoodscc.com/</t>
@@ -12740,14 +12432,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>bballmastery@gmail.com</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12760,7 +12449,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>info@northstarbasketball.ca</t>
@@ -12798,7 +12486,6 @@
           <t>oxfordheights@shaw.ca</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>https://oxfordheights.pointstreaksites.com/view/oxfordheights/sports-1/basketball-4</t>
@@ -12959,7 +12646,6 @@
           <t>Jarred Suyat, Diowe Bacanto, Jerrold Suyat — club contacts (PSO registry)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13019,7 +12705,6 @@
           <t>Tara Meneer — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13032,14 +12717,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>jbourcier28@gmail.com</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13062,7 +12744,6 @@
           <t>basketball@swcc1.ca</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
@@ -13090,7 +12771,6 @@
           <t>booking@swcc1.ca</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
@@ -13108,14 +12788,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>wpgwildcatsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13175,7 +12852,6 @@
           <t>Jordan Lopez — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13188,14 +12864,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>info@pegcityball.ca</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13250,7 +12923,6 @@
           <t>hello@visioneliteacademy.org</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>https://visioneliteacademy.org/basketball</t>
@@ -13268,7 +12940,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>bballwestside@gmail.com</t>
@@ -13279,7 +12950,6 @@
           <t>Clarence Vigilance, Coach</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13302,7 +12972,6 @@
           <t>Office@whyteridge.ca</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>https://whyteridge.ca/sports/basketball/</t>
@@ -13384,7 +13053,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>winnipegblizzards@gmail.com</t>
@@ -13412,7 +13080,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>chaoswinnipeg@gmail.com</t>
@@ -13440,14 +13107,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>jq14@shaw.ca</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13460,7 +13124,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>al.cox@uwinnipeg.ca</t>
@@ -13488,7 +13151,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>jrwesmen@gmail.com</t>
@@ -13548,14 +13210,11 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>wpgsaints@gmail.com</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13600,7 +13259,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>winnipegwolves@gmail.com</t>
@@ -13628,7 +13286,6 @@
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>worldclasshoopers@gmail.com</t>
@@ -13713,4 +13370,1091 @@
   <autoFilter ref="A1:F90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LWCC</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tyndall Park</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Attack Academy</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Southdale</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SWCC (South Winnipeg)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Relentless</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OHCC (Oxford Heights)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Empire</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dakota</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Garden City</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Evolve</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Junior Bisons</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KWCC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Whyte Ridge</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Central Plains</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Earl Grey</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rising Star</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Up Next</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>World Class</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Corydon</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Red River</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>East St Paul</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Maples</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RPCC</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Selkirk</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiefs</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Crossover</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REFRESH</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Triumph</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pythons</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LaSalle</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Riverview</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Girls Got Game</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NGCC</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Brokenhead Ballers</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Greendell</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Steinbach (Jr. Pilots)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winakwa</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>WMBA Fall/Winter Community Centre Leag=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ignite</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Westside</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DElite</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Downtown Dawgs</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Junior Legacy</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Attack South</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dynasty</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jr. Bobcats</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Peg City Club Basketball League (CBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dunk Dynasty</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Raptors</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Splash Bros</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bubble Bees</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Thrashers</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bucket Squad</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Terror Squad</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dark Knights</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Golden Snipers</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hoop Kings</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>HWE</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Splashers</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Strive Elite</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bam</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chuzz Elite</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Splash Zone</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>The Rec</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Prairie Basketball League (PBL)=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C71"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Manitoba.xlsx
+++ b/docs/research/provinces/SportsHub-Manitoba.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$90</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1614,6 +1621,9 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2103,6 +2113,9 @@
           <t>Appears only as a WMBA community-league team entry from Steinbach; may be an informal community program rather than incorporated club. WMBA also runs 'Community Youth Basketball' sessions in Steinbach (steinbachonline.com/events/222071).</t>
         </is>
       </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2227,6 +2240,9 @@
           <t>Instagram bio: 'club basketball program based out of Thompson, Manitoba'. Relationship to University of Manitoba Junior Bisons brand unclear (likely a northern namesake/affiliate). Only youth basketball club evidenced in Thompson; city otherwise offers courts via City of Thompson rec.</t>
         </is>
       </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3294,6 +3310,9 @@
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6868,6 +6887,9 @@
           <t>Type: private club/academy program. Founder Steven Wesley confirmed via Winnipeg Sea Bears 2026 coaching staff announcement ('He is also the founder of World Class Hoopers') — https://www.seabears.ca/winnipeg-sea-bears-announce-2026-coaching-staff. Email from Basketball Manitoba tryout announcement — https://www.basketballmanitoba.ca/2025/07/world-class-hoopers-announces-202526.html. No standalone website found; Instagram is primary presence. Registration via Google Forms (no commercial platform). Tryouts at Linden Woods Community Centre; 'Hooper Lab' winter training in South/Southwest/West Winnipeg (https://www.basketballmanitoba.ca/2026/01/world-class-hoopers-launches-hooper-lab.html). Teams compete in Peg City league (RAMP-hosted league pages, e.g. https://pegcityball.club/team/10819/3420/30195/264989).</t>
         </is>
       </c>
+      <c r="Q94" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7009,7 +7031,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P96"/>
+  <autoFilter ref="A1:Q96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Manitoba.xlsx
+++ b/docs/research/provinces/SportsHub-Manitoba.xlsx
@@ -441,7 +441,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,77 +471,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -556,42 +556,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Pembina Valley)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Altona</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://altonabasketball.com/</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Community youth basketball; fields tournament teams ($50/team entry incl. association T-shirt and Basketball Manitoba-provided injury insurance)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://altonabasketball.com/</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Listed as 'Altona Basketball Club' among orgs at Basketball Manitoba's 2019 Super Coaches Clinic; altonabasketball.com confirmed Manitoba (Basketball Manitoba insurance) but the domain did not resolve from this research environment — details from search-indexed site text. Not to be confused with Altona (Victoria, Australia) clubs.</t>
         </is>
@@ -608,47 +608,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Eastman)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Beausejour (Sunrise School Division area, exact town unconfirmed)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>mhovorka@sunrisesd.ca</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Mary-Jo Hovorka — listed contact (role not stated)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Boys basketball, ages 14-17 (per directory listing)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>community program (possibly school-community hybrid — contact uses Sunrise School Division email)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://nba.ecrew.ca/index.php?type=RE&amp;loc=en&amp;doprovince=MB&amp;v=m</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Surfaced in the NBA/eCrew 'Find a Place to Play' Manitoba directory as an Eastman-region boys 14-17 club; org name not published in accessible sources and the ecrew host did not resolve from this environment. Flag for manual follow-up; exclude from outreach until name/type confirmed (may be school-affiliated and out of scope).</t>
         </is>
@@ -665,62 +665,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Westman)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Healthy Living Centre, 2010 Louise Avenue, Brandon, MB</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>(204) 727-9756</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>cheungg@brandonu.ca</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>https://gobobcats.ca/</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Run by Brandon University Bobcats varsity basketball programs (coaching staff); no single named owner published</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Fall Bobcat Basketball Academy for Grades 5-8 (historically K-12); annual summer basketball camps; free annual Holiday Hoops youth camp (Grades 3/4-12) at the Healthy Living Centre</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>university-affiliated youth academy/camps (not school-board varsity)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2026/07/brandon-bobcats-basketball-academy-back.html</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Development academy + camps only; does not field club teams in youth leagues. Included as an academy-type program serving Brandon youth. | enriched 2026-07-18</t>
         </is>
@@ -737,62 +737,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Westman (West Region)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Brandon University (Henry Champ Gym / Healthy Living Centre South)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>(204) 727-9756</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>cheungg@brandonu.ca</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://gobobcats.ca/</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Affiliated with Brandon University Bobcats athletics</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Girls 14U, 16U, 17U club teams; tryouts at Henry Champ and HLC South</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>university-affiliated youth program</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?max-results=100</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -809,62 +809,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Westman (captured via league entrants)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Brandon University, Brandon, MB</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>(204) 727-7431</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>thomasn@brandonu.ca</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>http://www.gobobcats.ca/juniorbobcats</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Novell Thomas — Junior Bobcats Director &amp; BU Bobcats head coach</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Girls competitive spring program; high-level training plus tournaments/travel across MB and neighbouring provinces</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>university-affiliated club program</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>http://www.gobobcats.ca/juniorbobcats</t>
         </is>
@@ -881,67 +881,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Westman</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Healthy Living Centre, Brandon University, Brandon, MB (program venue)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>(204) 727-7431</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>thomasn@brandonu.ca</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://gobobcats.ca/juniorbobcats</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Novell Thomas — director &amp; coach (Brandon University women's basketball head coach)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Junior Bobcats: competitive spring club program for girls (14U/15U historically; 15U and 17U teams announced 2025), 2-3 practices/week plus travel tournaments; Bobcats Basketball Academy: fall/winter skills academy for boys &amp; girls grades K-12; spring break camps; hosts the Junior Bobcat Jamboree club tournament in Brandon</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Prairie Elite Basketball League (PEBL)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>university-affiliated youth club/academy</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://gobobcats.ca/juniorbobcats</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Fees ~$325+GST for club program (2020 page). PEBL is a league NOT in the already-mapped Manitoba list — new competitive-league discovery for the pipeline. Academy confirmed returning Fall 2026.</t>
         </is>
@@ -958,47 +958,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Westman (captured via PSO registry sweep)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>204-720-7778</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>treedell33@icloud.com</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Wardell Smith — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Boys team age 13</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -1015,67 +1015,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Westman (captured via PSO registry sweep)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Brandon</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>204-901-0360</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>wybamanitoba@hotmail.com</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://www.wyba.ca</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Juan Mosquera — association contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Regional youth leagues &amp; programs ages 13/15/17-18 boys &amp; girls (already-mapped league); also fields WYBA select teams</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Westman Youth Basketball Association (WYBA) leagues &amp; programs; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>community nonprofit / league operator with select teams</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>TeamLinkt (website, registration via app.teamlinkt.com, team app) — KEY COMPETITIVE INTEL</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Verification: "6 divisions, 300+ athletes" = May 2024 tournament (incl. girls); 2026 Club Tournament is boys-only, 3 divisions (U13/U15/U18), capped 12 teams/division, $700-750/team, May 15-17 2026 Brandon.</t>
         </is>
@@ -1092,57 +1092,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Parkland)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Dauphin</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>204-572-4484</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>john.marshall@mvsd.ca</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://www.facebook.com/DauphinHawksBasketball/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Division contacts (no president published): John Marshall (15U boys, 204-572-4484), Marc Giasson (18U boys, marc.giasson@mvsd.ca, 204-572-4241), Steph Lukye (14U girls, tcflukye@hotmail.com, 403-363-5050)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Club teams: 14U girls, 15U boys, 18U boys (Dauphin + Grandview); hosted club basketball tournament May 2022 for boys &amp; girls teams ages 14-18 ($350/team, 3-game guarantee)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>community club (volunteer-run; contacts use Mountain View School Division emails, but operates as a club, not a school team)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2022/04/dauphin-hawks-hosting-club-basketball.html</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Single primary source (PSO news, 2022) — current activity level unverified; Dauphin high-school 'Clippers' teams (MHSAA) excluded as school-board. Dauphin also hosted 2024 Manitoba Games basketball at Parkland Rec Complex. | Also listed as: Dauphin Hawks Basketball</t>
         </is>
@@ -1159,52 +1159,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Pembina Valley)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Morden</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>204-822-5431</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>recreation@mymorden.ca</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://morden.ca/recreation-organizations</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Municipal youth recreational basketball programming (youth rec basketball; 12+ basketball) offered through City of Morden recreation</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>municipal recreation program (no dedicated club found in Morden)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://morden.ca/recreation-organizations</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>No standalone youth basketball club found for Morden after PSO-registry sweep + local searches; club-level players in Morden are served by nearby Winkler Basketball Club (Pembina Valley) and school (MHSAA) programs, which are out of scope. Included so the pipeline records Morden coverage. | enriched 2026-07-18</t>
         </is>
@@ -1221,57 +1221,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>South Region (Eastman)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Niverville</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Niverville Recreation Centre area (tryouts at 501 Centre St, Niverville)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>204-388-4600</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>recreation@whereyoubelong.ca</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Boys club teams born 2010-2013; coach with Los Angeles background; venue Niverville Recreation Centre</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Registration form (online)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2024/07/aim-high-basketball-academy-hosting.html</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -1288,72 +1288,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Eastman</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Niverville</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Niverville Community Resource &amp; Recreation Centre, 501 Centre St., Niverville, MB</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>204-925-5774</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>info@wmba.ca</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://www.nivervillerecreation.com/index.html</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Darcy Coss — WMBA program contact for Niverville</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Community youth basketball for boys &amp; girls ages 4-18 delivered in partnership with the Winnipeg Minor Basketball Association at the Niverville CRRC; Niverville is a WMBA catchment area</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community program (municipal rec / WMBA satellite)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>RAMP (WMBA registration via rampregistrations.com/winnipegminorbasketball)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://steinbachonline.com/events/222073</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Not an independent club — WMBA satellite/catchment program run with Niverville Recreation. WMBA also advertised 'Community Youth Basketball with the WMBA' events in the Steinbach area (SteinbachOnline events 222073/222074, pages since expired), indicating WMBA rural-satellite expansion into Eastman towns — relevant competitive intel. Manitoba Magic (Winnipeg club) also runs summer camps at Niverville Rec Centre.</t>
         </is>
@@ -1370,57 +1370,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Eastman (south of Winnipeg)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Niverville</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Niverville CRRC, 501 Centre St., Niverville, MB</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>204-388-4600 ext 3</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>recreation@whereyoubelong.ca</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>https://nivervillerec.ca/programs/</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Weekly instructional youth basketball ages 6–9 and 9–14 at the CRRC; hosts Jr. NBA Youth Basketball Camp (ages 5–12)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>town recreation program (multi-sport org)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://nivervillerec.ca/programs/</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Type: municipal community recreation program (Town of Niverville Recreation &amp; Wellness — 'whereyoubelong.ca' is the town domain), not a rep club. Email was Cloudflare-obfuscated on site; decoded from page source (also feedback@whereyoubelong.ca). No named recreation director/coordinator published on site. Platform intel: registration via PerfectMind (townofniverville.perfectmind.com). Sources: https://nivervillerec.ca/contact-us/ and https://nivervillerec.ca/programs/.</t>
         </is>
@@ -1437,57 +1437,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Eastman)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Niverville</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Niverville Community Resource &amp; Recreation Centre, Niverville, MB (program venue)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Community youth basketball for boys and girls ages 4-18, delivered in Niverville under the Winnipeg Minor Basketball Association's community programming at the Niverville CRRC</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>community program (WMBA satellite; no standalone incorporated club found)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>RAMP InterActive (via WMBA)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://nba.ecrew.ca/index.php?type=RE&amp;loc=en&amp;doprovince=MB&amp;v=m</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>NBA/eCrew 'Find a Place to Play' directory lists a Niverville club for boys &amp; girls 4-18 with contact via WMBA; SteinbachOnline lists 'Community Youth Basketball with the WMBA' events in the area. Evidence of WMBA expanding rural Eastman programming rather than an independent club.</t>
         </is>
@@ -1504,57 +1504,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Eastman/Central (south of Winnipeg)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Niverville area (Eastman/Central region)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>204-998-4462</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>prairiebasketballleague@gmail.com</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>https://prairiebasketballleague.ca</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Abram Razon — organizer (PSO registry contact)</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Regional league ages 7–19+ boys &amp; girls (already-mapped league) plus PBL Select rep teams that compete in Winnipeg club competition</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Prairie Basketball League (PBL); Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>community nonprofit / league operator with select teams</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -1571,58 +1571,58 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Central Plains (west of Winnipeg)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Portage la Prairie</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>204-870-1071</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>centralplainsbasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Darin Arnold — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Boys &amp; girls rep teams ages 13–18</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials); Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1636,47 +1636,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Interlake (north of Winnipeg)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Selkirk</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Blake Hamm — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Boys rep teams ages 13–16</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -1693,62 +1693,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Interlake/East)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Selkirk</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lord Selkirk Regional Comprehensive Secondary School, 221 Mercy Street, Selkirk, MB (program base)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>selkirkroyalsbb@outlook.com</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2018/03/selkirk-junior-royals-basketball-club.html</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Blake Hamm — primary club contact (PSO registry &amp; directory); programs led by Dean Goodbrandson, LSRCSS Royals Varsity Boys Head Coach</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Boys club teams U13, U14, U15, U16 (directory listing; 15U/17U teams active at provincials); annual Spring Break camp Grades 5-11; summer camp Grades 5-8; hosts spring club tournament for boys 15U &amp; 17U</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>community nonprofit (feeder club aligned with Lord Selkirk Regional 'Royals' school program but operated as a Basketball Manitoba member club)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Instagram @selkirkjuniorroyals. Included as a club (community rep club + camps), distinct from the LSRCSS varsity program itself.</t>
         </is>
@@ -1765,47 +1765,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>South Region (Pembina Valley)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Southern Manitoba (Winkler/Morden area)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>stephen@bigcountrybasketball.com</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>https://www.bigcountrybasketball.com/</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Stephen Lameroux — contact/lead</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Girls club program ages 12-17 plus basketball-specific training &amp; development for all levels (LTAD-based holistic model)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>private club/training program</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://www.bigcountrybasketball.com/about</t>
         </is>
@@ -1822,67 +1822,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Eastman/Central 'South Region')</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>204-998-4462</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>prairiebasketballleague@gmail.com</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://prairiebasketballleague.ca/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Abram Razon — Commissioner (staff: Allan Cua scheduling manager, Eliel Badiola volunteer coordinator, Kim Fortuno head referee, Mike Page youth program director)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Spring League, Summer League ('Battlegrounds' + tournament), Winter League; 'Select' club-team program; youth coaching/training programs</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Prairie Basketball League (PBL); Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>community org / league operator (also listed in Basketball Manitoba club database as a club entity)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Custom website (prairiebasketballleague.ca); registration platform not identified</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://prairiebasketballleague.ca/</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>PBL is already a mapped league; included here because the PSO club database lists it as the club-level entity for the South Region and it fields its own Select teams. Winter league registration deadline Aug 1. | Also listed as: Prairie Basketball League (PBL)</t>
         </is>
@@ -1899,67 +1899,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Eastman / Central</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>204-998-4462</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>prairiebasketballleague@gmail.com</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>https://prairiebasketballleague.ca</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Abram Razon — commissioner (oversees club teams, finances, registration, sponsorships); Mike Page — youth program director</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Ages 7-19+ per PSO directory; three seasonal community leagues (spring, winter, summer incl. 'Battlegrounds' tournaments) plus community youth programs and training for the Eastman/Central regions</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Prairie Basketball League (PBL)</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>community league organization (nonprofit-style, league operator)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Squarespace (website); registration platform not identified</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://prairiebasketballleague.ca/contactus</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Included as an organization entry because it is in the PSO club directory and runs youth programs directly, not just the (already-mapped) league. Other staff: Allan Cua (scheduling), Eliel Badiola (volunteers/stats), Kim Fortuno (head referee). Facebook handle 'Pblsteinbach' confirms Steinbach base.</t>
         </is>
@@ -1976,62 +1976,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Eastman</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>jdykerman@hsd.ca</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>http://www.southeaststormbasketball.com/</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Darcy Coss — contact (per regional listing)</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Registered non-profit club; boys &amp; girls approx. ages 8-18; teams practice in Steinbach and area and travel to Winnipeg for league play; registered member of Basketball Manitoba</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>WMBA league play registered via RAMP (wmba.ca is RAMP InterActive)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>http://www.southeaststormbasketball.com/</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Club website domain currently not resolving (DNS failure Jul 2026) though still Google-indexed with About page listing an executive board; Facebook page active as 'Southeast Community Storm Basketball'. Executive names not retrievable — do not have principal. | Also listed as: Southeast Storm Basketball</t>
         </is>
@@ -2048,73 +2048,73 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Eastman)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Steinbach</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>204-370-6507</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>wayneelias@outlook.com</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/team/13441/506/7616/366710</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Wayne Elias — Head Coach (listed contact on WMBA team page; org structure behind team not published)</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Community rep team(s): 15-17 Girls entered in WMBA Community League (Winter)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>community program (single-team community entry; club status unclear)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>RAMP InterActive (via WMBA league website)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/team/13441/506/7616/366710</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Appears only as a WMBA community-league team entry from Steinbach; may be an informal community program rather than incorporated club. WMBA also runs 'Community Youth Basketball' sessions in Steinbach (steinbachonline.com/events/222071).</t>
         </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2128,57 +2128,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>North Region (Norman)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>The Pas</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>204-620-6110</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>thepasbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://thepasbasketball.ca/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Darcy Hanchuk — PSO directory contact</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Youth basketball association programming for The Pas &amp; area (northern Manitoba)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory?max-results=100</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Encountered via PSO registry sweep; outside Winnipeg region proper</t>
         </is>
@@ -2195,53 +2195,53 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Northern)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Thompson</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>https://www.instagram.com/juniorbisons/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Kristin Donovan — listed contact for Thompson girls club (ages 13-17) in the NBA/eCrew 'Find a Place to Play' Manitoba directory</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Club basketball program based in Thompson; girls club ages 13-17 listed; Junior Bison Thompson athletes received member pricing at Prairie Elite Academy camps held at Wapanohk Community School (Grades 5-12)</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://www.instagram.com/juniorbisons/</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Instagram bio: 'club basketball program based out of Thompson, Manitoba'. Relationship to University of Manitoba Junior Bisons brand unclear (likely a northern namesake/affiliate). Only youth basketball club evidenced in Thompson; city otherwise offers courts via City of Thompson rec.</t>
         </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2255,62 +2255,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>West St. Paul (Winnipeg metro)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>#8 Unit-E, Third St on Emes Road, West St. Paul, MB R2P 1L4</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>204-891-0144</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>btbdhoops@gmail.com</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://btbdhoopsxrelentless.ca/</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>John Sumugat — PSO directory contact; 'Coach Patrick' listed on 2026 tryout notice (relentlessbasketball.wpg@gmail.com)</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Private training gym (skills, S&amp;C, mindfulness, online) plus Relentless club teams boys/girls born 2009-2016; co-ed ages 12-17 per directory</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Sea Bears Youth League (SBYL) 3x3 Series</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>private academy/training + club</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://btbdhoopsxrelentless.ca/</t>
         </is>
@@ -2327,52 +2327,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Pembina Valley / Central</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Winkler</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>prairieelitebasketballacademy@gmail.com</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>https://www.facebook.com/prairieelitebasketball/</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>JP Beauchemin — co-founder (former U of Manitoba women's assistant coach); Victoria Zuke — co-founder (former Westwood Collegiate varsity assistant coach)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Female-focused training academy: development camps for girls Grades 7-12 and players camps for boys &amp; girls ages 11-18 held in Winkler (2018); ran 'Prairie Elite South' club team tryouts in Winkler for girls born 2002+ (2019)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2018/11/prairie-elite-basketball-academy.html</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Most recent activity found is 2019 — likely dormant/defunct; include for completeness. Founders are Winnipeg-based coaches; Winkler was primary delivery site.</t>
         </is>
@@ -2389,62 +2389,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Pembina Valley)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Winkler</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>winklerbasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>https://www.facebook.com/winklerbasketballclub/</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Walter (Walt) Giesbrecht — long-time club organizer (also Garden Valley Collegiate coach); Mark Hamm — club coach</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Boys &amp; girls club (rep) teams across ages incl. 14U boys, 16U girls, 16U/17U boys; annual fall skill-development sessions Grades K-8 ($65 incl. T-shirt, Oct-Nov); longstanding boys &amp; girls club basketball tradition</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Peg City Club Basketball League (CBL); Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>None found — registration by e-transfer to winklerbasketballclub@gmail.com; Facebook/Instagram (@winklerbasketballclub) for comms</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://www.pembinavalleyonline.com/articles/winkler-basketball-club-continues-to-flourish</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Partnering with City of Winkler + Winkler Pickleball on a $1.5M indoor court facility (city funding approved). Also serves Morden/Pembina Valley youth. Closely linked to Winkler Minor Basketball (announces its registration).</t>
         </is>
@@ -2461,57 +2461,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Rest of Manitoba (Pembina Valley)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Winkler</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>winklerminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://winklerminorbasketball.weebly.com/</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Spring house league (begins March) for Winkler &amp; area, boys and girls divisions Grades 3&amp;4, 5&amp;6, 7&amp;8; registration $75; mission: promote basketball skill development in young athletes in the Winkler area</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Winkler Minor Basketball spring house league (own)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>community nonprofit (house-league arm, affiliated with Winkler Basketball Club)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Weebly website; org page also exists on SportsEngine (sportsengine.com/org/winkler-minor-basketball); registration announced via Instagram @winklerminorbasketball</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://winklerminorbasketball.weebly.com/</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Registration historically taken in person at Garden Valley Collegiate lobby and promoted through Winkler Basketball Club's Facebook — the two orgs are affiliated (rep club vs house league). SportsEngine listing = software intel. | Also listed as: Winkler Minor Basketball</t>
         </is>
@@ -2528,57 +2528,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>204elite@gmail.com</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>https://www.instagram.com/204elite/</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Dan Becker — club lead (NCCP Level 4 coach, ex-NCAA D1 and pro)</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Nonprofit boys club; trains 3–4x/week; Canadian and US AAU tournament schedule</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2022/06/204-elite-basketball-club-hosting.html</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Type: private rep/club program (boys). Dan Becker (NCCP Level 4, ex-NCAA D1/pro player) and email confirmed via Basketball Manitoba tryout announcements — https://www.basketballmanitoba.ca/2023/06/204-elite-basketball-club-is-hosting.html and https://www.basketballmanitoba.ca/2022/06/204-elite-basketball-club-hosting.html. No standalone website found; Instagram primary. Registration by email (no commercial platform). Competes in Peg City Youth League (RAMP) and AAU events in USA. | Also listed as: 204 Elite</t>
         </is>
@@ -2595,47 +2595,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>ambush.club.basketball@gmail.com</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Jaira Labelle — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Boys &amp; girls rep teams ages 11–16; multiple teams per age (Gold/Knights/Raiders/Ghosts/Pirates)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials); Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -2652,52 +2652,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>atlasbball@gmail.com</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>https://www.atlasbasketball.com</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Matthew Dyck — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Boys rep teams ages 12, 14, 18+ (two-team age groups Black/Gold)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -2714,62 +2714,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Winnipeg (North)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>431-999-7269</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>sukhvir.singh@attackbball.ca</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>https://www.attackbball.ca</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Sukhvir Singh — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Community skill development ages 5–18 (Amber Trails School, Salisbury Morse Place, South End, West End Athletics sites); Attack Academy elite club teams; ages 7–19+, boys &amp; girls; summer programs; Canada Basketball Verified</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials); Attack Basketball community league (own)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>One of the largest Winnipeg clubs — swept both Tier 1 provincial titles it entered in 2026</t>
         </is>
@@ -2786,57 +2786,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Winnipeg (South)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>attacksouthbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Tara Kelly, Erin Sheldon, Ogo Okwumabua — club contacts (PSO registry)</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Girls rep teams ages 12–15</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Google Forms registration</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Girls-only club; separate PSO registry entry from Attack Basketball</t>
         </is>
@@ -2853,37 +2853,37 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Boys 18U club team; tryouts at Sturgeon Heights Community Centre</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>JotForm registration</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2024-07-17T00:00:00-05:00&amp;max-results=50</t>
         </is>
@@ -2900,47 +2900,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Winnipeg / Interlake</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>info@chiefsbball.club</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Indigenous-focused club in partnership with Interlake Reserve Tribal Council (IRTC); boys &amp; girls born 2011-2013 (earlier U12); low-cost $10 tryouts at Université de Saint-Boniface; IRTC Chiefs also field U21 travel teams for Alberta Indigenous Games</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Peg City Club Basketball League (CBL); Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>community nonprofit (Indigenous partnership)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/07/chiefs-basketball-announces-august-2025.html</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Also listed as: Chiefs Basketball</t>
         </is>
@@ -2957,72 +2957,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Winnipeg (River Heights/Crescentwood)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>1370 Grosvenor Ave, Winnipeg, MB</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>204-488-7000</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>corydon@wmba.ca</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>https://corydoncc.com/programs/sports/basketball/</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Abbie Bajon (General Manager)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://corydoncc.com/programs/sports/basketball/</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Type: community association, three sites: River Heights 1370 Grosvenor Ave; Crescentwood 1170 Corydon Ave; Sir John Franklin 1 Sir John Franklin Rd. Basketball email (convenor) corydon@wmba.ca; program run through WMBA community league (RAMP InterActive). GM Abbie Bajon abajon@corydoncc.com (204) 488-7000 ext 202; Board President Steve Wach; Program Coordinator Christine Kieloch ckieloch@corydoncc.com ext 203. Sources: https://corydoncc.com/programs/sports/basketball/, https://corydoncc.com/about-corydon/staff/, https://corydoncc.com/about-corydon/board/.</t>
         </is>
@@ -3039,67 +3039,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>204-500-9033</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>crossoverwinnipeg@gmail.com</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>https://www.crossoverwinnipeg.ca/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Ricardo Martinez — Founder (also named head coach of RRC Polytech Rebels men's program 2026-27)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Elite rep club teams boys &amp; girls born 2008-2015 (ages ~10-18); summer camps (XVR Summer Camp); online training; Canada Basketball Verified Organization; LTAD model</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Manitoba Basketball Club Championships (provincials); Peg City Showcase</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>private club/academy</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>SquadLocker (team store); tryout registration via own site</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>PSO directory lists as Canada Verified Organization, Winnipeg city-wide</t>
         </is>
@@ -3116,57 +3116,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>431-334-5169</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>delitembb@gmail.com</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Anton Dziuba — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Boys rep teams, birth years 2008–2012 (registry ages 15–18)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Google/JotForm registration forms per tryout posts</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -3183,72 +3183,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Winnipeg (St. Vital South)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>1188 Dakota Street, Winnipeg, MB R2N 3H4</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>204-254-1010</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>michele@dakotacc.com</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://www.dakotacc.com/121/basketball</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Michele Augert — President &amp; CEO</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>WMBA Community League basketball for Dakota catchment; 3-court fieldhouse (Jonathan Toews Sportsplex)</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://www.dakotacc.com/121/basketball</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Type: community centre (large multi-facility org incl. $20.5M fieldhouse). Email listed is the CEO's (from staff page); no general inbox published. Board Chair: Cory Shangreaux; Director Programming &amp; Operations: Mike Whalen (mikew@dakotacc.com). CAUTION: census URL /121/basketball now 404s and basketball is no longer listed among programs (hockey/pickleball/soccer/volleyball) — program status needs re-verification. Competitive intel: uses ActiveNet/ActiveCommunities registration (anc.ca.apm.activecommunities.com/dakotacc) + has a SportsEngine org page. Sources: https://dakotacc.com/about/staff/ ; https://dakotacc.com/6/board-of-directors ; https://dakotacc.com/contact</t>
         </is>
@@ -3265,53 +3265,53 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>downtowndawgs@outlook.com</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Jordan Fotheringham — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Boys rep teams ages 13 and 16</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3325,52 +3325,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>dynastywpg@gmail.com</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Girls rep teams, born 2009–2012; tryouts at Sport Manitoba (145 Pacific Ave)</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Google Forms (tryout registration)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/07/dynasty-basketball-announces-tryouts.html</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Type: private club program (girls, birth years 2009-2012). Email from Basketball Manitoba tryout announcement — https://www.basketballmanitoba.ca/2025/07/dynasty-basketball-announces-tryouts.html — and confirmed on their tryout Google Form (e-transfer payments to dynastywpg@gmail.com). Tryouts held at Sport Manitoba, 145 Pacific Avenue (rented court, not club address). Facebook: https://www.facebook.com/DynastyWpg/ and https://www.facebook.com/TeamDynastyBasketball/. No website; registration via Google Forms. No founder/coach names published anywhere found.</t>
         </is>
@@ -3387,52 +3387,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Winnipeg (central)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>145 Pacific Avenue, Winnipeg, Manitoba R3B 2Z6</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>empireelitehoops@gmail.com</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Boys teams born 2008–2014, girls born 2010–2012; trains at BATTLE 204 facility; local, national and USA tournaments; tryouts at Sport for Life Centre and YFC Winnipeg</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Peg City Showcase; Peg City Club Basketball League (CBL); Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>community club (nonprofit status unverified)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/07/empire-basketball-club-tryouts-set-for.html</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Not in PSO club registry despite being one of the most successful clubs — registry is incomplete | Also listed as: Empire Basketball Club | enriched 2026-07-18</t>
         </is>
@@ -3449,67 +3449,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Université de Saint-Boniface, 195 Rue Despins, Winnipeg, MB (training base)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>204-292-4805</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>nicholas@evolvebasketball.ca</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>https://www.winnipegsportinstitute.com</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Nicholas Lother — director/contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Club teams boys &amp; girls ages 7–19+; training programs; 'Bridge the Gap' program</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Online registration via own site (info@winnipegsportinstitute.com)</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -3526,72 +3526,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Winnipeg (North — Garden City)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>725 Kingsbury Ave, Winnipeg, MB R2V 3H9</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>204-940-6111</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>info@gardencitycc.com</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>https://www.gardencitycc.com/garden-city-sports-camps/basketball</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Andy Haworth — Board President</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Basketball camps and community basketball; WMBA catchment centre</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>SportsEngine (org page at sportsengine.com/org/garden-city-community-centre); WMBA league ops on RAMP</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://www.gardencitycc.com/garden-city-sports-camps/basketball</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>SportsEngine presence is competitive-intel-relevant | Type: community centre. Basketball Director-at-Large: Ron Quintana (also 2nd Vice President). General Manager: Margie Reis (gm@gardencitycc.com). Registration via WMBA (wmba.ca); also has a SportsEngine org page (competitive intel). Sources: https://www.gardencitycc.com/gccc-about/boardofdirectors ; https://www.gardencitycc.com/gccc-about/management-team ; https://www.gardencitycc.com/garden-city-sports-camps/basketball</t>
         </is>
@@ -3608,72 +3608,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Winnipeg (Northeast — North Kildonan)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>1717 Gateway Road, Winnipeg, MB R2G 4H1</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>(204) 982-1234</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>youthbasketball@hotmail.ca</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>https://gatewayrec.com/sport-programs/basketball/</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Denis Van Laeken (General Manager)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://gatewayrec.com/sport-programs/basketball/</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Type: community association / recreation centre. Basketball Convenor: Mike Catalano youthbasketball@hotmail.ca (registration limited to Gateway catchment area; online registration). Board President: Len Fabris (204) 669-0694; GM Denis Van Laeken gm@gatewayrec.com ext 1; Office Manager Sherri Quesnel admin@gatewayrec.com ext 2. Plays in WMBA community league. Sources: https://gatewayrec.com/sport-programs/basketball/, https://gatewayrec.com/contact-us/.</t>
         </is>
@@ -3690,62 +3690,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Winnipeg (Southwest)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>ignitebasketballwinnipeg@gmail.com</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>https://www.ignitecanadabasketball.com</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Coach Charles and Coach Michelle — founders (family-run since 2014; surnames not published)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Boys club teams born 2008–2013 (multiple teams per age); girls historically; practices 2–3x/week in south Winnipeg gyms; tryouts third week of August</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>community club (nonprofit status unverified)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Google Forms registration; Hudl for team film</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://www.ignitecanadabasketball.com/about-ignite</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>Type: private club program, south Winnipeg. Primary contact Charles Carlos + email from Basketball Manitoba club listing — https://www.basketballmanitoba.ca/2016/06/ignite-canada-basketball-club.html. Co-founded by 'Coach Charles and Coach Michelle' (Michelle's surname unverified — do not assume). Website root returned 404 to automated fetch but pages remain indexed (https://www.ignitecanadabasketball.com/about-ignite); Facebook https://www.facebook.com/ignitecanadabasketball/. 2025-26 tryouts at Canadian Mennonite University, 500 Shaftesbury Blvd; Google Forms registration — https://www.basketballmanitoba.ca/2025/07/ignite-canada-basketball-announces.html.</t>
         </is>
@@ -3762,37 +3762,37 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>junioralliancebasketball@gmail.com</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Boys born 2008-2014 and girls born 2009 club teams; tryouts at Red River College Polytech South Gym</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2025-07-02T00:00:00-05:00&amp;max-results=50</t>
         </is>
@@ -3809,52 +3809,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>juniorbisonboysbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>https://www.juniorbisonboys.ca/</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Youth basketball club offering programming to boys ages 12-17</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>SportsEngine (org listing/registration)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://www.sportsengine.com/org/junior-bison-boys-basketball-club</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Possibly related to/predecessor of UM Junior Bisons program; own domain did not resolve at research time — treat as needs-confirmation | enriched 2026-07-18</t>
         </is>
@@ -3871,72 +3871,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Winnipeg (South — Fort Garry)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>University of Manitoba, Winnipeg, MB</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>204-474-7279</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>junior.bisons@umanitoba.ca</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>https://umanitoba.ca/junior-bisons/junior-bisons-basketball</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Michele Sung (Bisons women's head coach) and Kirby Schepp (Bisons men's head coach) — program directors</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Club teams ages 10–18 boys &amp; girls (~$1,455/yr); girls youth league ages 5–11; high-performance summer camps 12–18; Level Up elite skills training</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Peg City Club Basketball League (CBL); Peg City Showcase; Prairie Elite Basketball League (PEBL); Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>university-affiliated club program</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>UM Sport &amp; Rec online portal (sportandrec.umanitoba.ca)</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://umanitoba.ca/junior-bisons/junior-bisons-basketball</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Type: university-run youth development program (not a private club) — programs run at Frank Kennedy Centre, facilitated by Bisons student-athletes; camps led by Bisons varsity head coaches Kirby Schepp (men) and Michele Sung (women), no dedicated youth-program coordinator named. Contact block (email, program office phone 204-474-7279, registration desk 204-474-6100, Max Bell Centre address) from https://umanitoba.ca/mini-u/junior-bisons. Competitive intel: registration via UM's own sport-and-rec system at sportandrec.umanitoba.ca (institutional rec-management platform, not RAMP/TeamLinkt).</t>
         </is>
@@ -3953,72 +3953,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Winnipeg (West — Kirkfield/Westwood)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>165 Sansome Ave, Winnipeg, MB R3K 0N8</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>204-832-1175</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>office@kwcc.net</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>https://www.kirkfieldwestwood.com/basketball/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Sarah Buchan — President (president.sb@kwcc.net)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>WMBA basketball, no tryouts/no experience necessary; outdoor court (built 2011) hosts WMBA x ELEVATE 3x3 summer league</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA x ELEVATE 3x3 Youth Summer League</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://www.kirkfieldwestwood.com/basketball/</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Type: community centre. Basketball Convenor: Aaron Russell (basketball@kwcc.net). Program plays out of Keith Bodley Arena (same 165 Sansome Ave site); satellite location 3160 McBey Ave R3K 0T7. Registration via WMBA (wmba.ca); no-tryout recreational program. Operations Supervisor: Jamie Jamieson. Sources: https://www.kirkfieldwestwood.com/board-of-directors/ ; https://www.kirkfieldwestwood.com/contact/ ; https://www.kirkfieldwestwood.com/basketball/</t>
         </is>
@@ -4035,67 +4035,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Winnipeg (St. James / West)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>165 Sansome Ave, Winnipeg, MB R3K 0N8</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>(204) 832-0038</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>office@kwcc.net</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>https://www.kirkfieldwestwood.com/</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>WMBA founding community centre (1997); WMBA Foundation outdoor courts on site; fields WMBA catchment teams</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>multi-sport community centre</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>RAMP (via WMBA)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://www.wmba25.ca/about</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -4112,62 +4112,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>mkraus.legacyprep@gmail.com</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>https://legacypreparatorybasketballacademy.ca/</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Marlin Kraus — PSO directory contact / program lead</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Founded 2020. Prep program U21 for HS seniors/postgrads; Legacy Club program 15U-18U boys; Junior Legacy club teams boys born 2009-2014; prep team training</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Select Prep League; DIME Basketball; Canadian Junior Basketball League (CJBL); Peg City Showcase; DIME league</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Google Forms applications; alt email info@legacyPBA.com</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://legacypreparatorybasketballacademy.ca/</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Also listed as: Legacy Preparatory Basketball Academy</t>
         </is>
@@ -4184,67 +4184,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Winnipeg (Linden Woods / SW)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>414 Lindenwood Dr W, Winnipeg</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>(204) 487-2435</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>manager@lindenwoodscc.com</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>https://lindenwoodscc.com/</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>WMBA founding community centre (1997); current WMBA indoor court venue; hosts club tryouts (World Class Hoopers, Ignite, Triumph)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>multi-sport community centre</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>RAMP (via WMBA)</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>https://wmba.ca/locations</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -4261,62 +4261,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>204-292-3018</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>mbmagicbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>https://mbmagicbball.com</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Arsenio dela Cruz, Club Contact</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Non-profit volunteer-run club founded 2002; ages 7–17 boys &amp; girls; training camps ($150/8 sessions); travel teams to showcases/tournaments</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://mbmagicbball.com/</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -4333,62 +4333,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>204-292-3018</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>info@mbmagicbball.com</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>https://mbmagicbball.com/</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Arsenio dela Cruz, Club Contact</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Nonprofit est. 2002, 100% volunteer-run; boys &amp; girls ages 7-17; rep teams (tryouts born 2006-2016 at CMU / Norberry-Glenlee CC); development camps ($150/8 sessions); showcase &amp; tournament travel</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Peg City Club Basketball League (CBL); Sea Bears Youth League (SBYL) 3x3 Series</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://mbmagicbball.com/</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Alt email seen: mbmagicbasketball@gmail.com | enriched 2026-07-18</t>
         </is>
@@ -4405,72 +4405,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Winnipeg (Maples / NW)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>434 Adsum Drive, Winnipeg, MB R2P 1J1</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>204-953-1190</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>office@maplescc.ca</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>https://maplescc.ca/programs/basketball/</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Basketball Convenor &amp; Head Coach position vacant at research time — inquiries to office</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>WMBA catchment basketball: 7-8 co-ed 3v3, 9-10 4v4, 11-12 and 13-17 5v5; WMBA league fees ~$285 + club fees</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>multi-sport community centre</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>RAMP (via WMBA)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://maplescc.ca/programs/basketball/</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Type: community centre (legal entity: Maples Recreation Assoc. Inc., est. 1973). 'Basketball Convenor &amp; Head Coach' position listed as VACANT on program page. Board names not published (governed by volunteer Board + GM per https://maplescc.ca/about/); no current president name found (BBB lists Dan Ricard only for 2009/2010 — stale, not used). Registration via WMBA (wmba.ca). Multiplex: 204-953-1191 / arena@maplescc.ca. Sources: https://maplescc.ca/programs/basketball/ ; https://maplescc.ca/about/</t>
         </is>
@@ -4487,37 +4487,37 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>bballmastery@gmail.com</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Boys &amp; girls club teams born 2009; Instagram @masterybasketball</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2023-12-14T00:00:00-06:00&amp;max-results=50</t>
         </is>
@@ -4534,57 +4534,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>info@northstarbasketball.ca</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>https://www.northstarbasketball.ca/</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Daron Leonard — Founder &amp; Executive Director / Head Coach (est. foundation 2015; ex-Carleton Ravens, pro overseas)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Nonprofit Northstar Sports Foundation operates Elite Performance Academy (all skill levels), Northstar Preparatory Institute (elite HS prep, men's &amp; women's teams), youth camps and individual training</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>National Preparatory Association (NPA)</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>private academy operated by nonprofit foundation</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>https://www.northstarbasketball.ca/about</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -4601,67 +4601,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Winnipeg (Transcona)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>359 Dowling Ave E, Winnipeg, MB R2C 3M4</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>204-222-2419</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>oxfordheights@shaw.ca</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>https://oxfordheights.pointstreaksites.com/view/oxfordheights/sports-1/basketball-4</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Transcona-area catchment for WMBA basketball; outdoor court (built 2014) hosts WMBA x ELEVATE 3x3 summer league</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA x ELEVATE 3x3 Youth Summer League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Pointstreak Sites (club website); WMBA league ops on RAMP</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>https://oxfordheights.pointstreaksites.com/view/oxfordheights/sports-1/basketball-4</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Pointstreak Sites usage is competitive-intel-relevant | Type: community club (Transcona-area WMBA basketball catchment). Basketball program email: ohccbasketball@shaw.ca. No president name published — club was actively recruiting President, VP &amp; Treasurer per its Facebook page. CAUTION: census URL (oxfordheights.pointstreaksites.com) is DEAD — 301 redirects to stacksports.com (Pointstreak sites decommissioned); current site oxfordheights.ca has broken SSL (http only) + active Facebook page facebook.com/p/Oxford-Heights-Community-Club-100063608951700/. Sources: http://oxfordheights.ca/contact.html ; https://www.yellowpages.ca/bus/Manitoba/Winnipeg/Oxford-Heights-Community-Club/2448377.html</t>
         </is>
@@ -4678,62 +4678,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>204-294-7931</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>pbawpg@gmail.com</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>https://pbawpginc.ca/</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Contacts: Manny Aranez (204-294-7931), Muriel Masangkay (204-294-7921)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>LEAGUE OPERATOR: recreational Filipino-community league; Youth Divisions boys &amp; girls born 2008-2015 plus Juvenile (2005-2007); Fall/Winter seasons; youth club teams must register with Basketball Manitoba first</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>PBA Winnipeg (Philippine Basketball Association of Winnipeg) — Youth Divisions</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>community nonprofit league operator</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Online registration at pbawpginc.ca</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2024/08/pba-winnipeg-announces-2024-25.html</t>
         </is>
@@ -4750,11 +4750,6 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>Winnipeg</t>
@@ -4762,60 +4757,65 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>145 Pacific Ave, Winnipeg, MB R3B 2Z6</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>204-925-5775</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>info@pegcityball.ca</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>https://pegcityball.club/</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Operated by Basketball Manitoba (PSO), same address/office</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>LEAGUE OPERATOR: Peg City Club Basketball League CBL (10U-13U), Peg City Showcase (14U-17U), SBYL 3x3 Series (7U-18U), Target Score Spring Series; hub for 175+ competitive club teams; also adult senior league (pegcityball.ca)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Peg City Club Basketball League (CBL); Peg City Showcase; Sea Bears Youth League (SBYL)</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>PSO-operated league</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>RAMP InterActive</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://pegcityball.club/content/club-basketball-overview</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Sea Bears Youth League is fully managed by Peg City Basketball in partnership with CEBL's Winnipeg Sea Bears (launched April 2025, ages 7-14, Elite + Developmental divisions)</t>
         </is>
@@ -4832,42 +4832,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Boys rep (17U entry in fall league); U18 team referenced in coach bios</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/09/schedules-announced-for-peg-city.html</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Real league entrant but no club web presence found; do not confuse with US 'Quest Basketball' orgs | NO VERIFIABLE EVIDENCE FOUND for a Winnipeg/Manitoba club by this name: no Basketball Manitoba announcements, no Peg City league presence, no social pages, no registration pages located across multiple searches. questbasketball.com appears in search results but returned 403 and could not be confirmed as Manitoba-related ('Quest' also collides with Canada Basketball's 3x3 Canada Quest event series, a likely source of the original listing confusion — https://www.basketball.ca/en/development/3x3-canada-quest). Flag for manual review / possible removal from the census.</t>
         </is>
@@ -4884,62 +4884,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t>204-995-1682</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>refreshbasketballywg@gmail.com</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>https://linktr.ee/refreshbasketball</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Ryan Reyes — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Youth development and rep teams ages 14–19+, boys &amp; girls; PRIME program partnership</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Linktree + bit.ly registration links</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -4956,57 +4956,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>204-891-0144</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>btbdhoops@gmail.com</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>https://www.btbdhoopsxrelentless.ca</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>John Sumugat — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Boys &amp; girls rep teams ages 12–17; multiple regional teams (East/West/South)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -5023,57 +5023,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>204-951-2070</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>wpgrisingstarclub@gmail.com</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Jarred Suyat, Diowe Bacanto, Jerrold Suyat — club contacts (PSO registry)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Rep teams ages 9–18, boys &amp; girls</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials)</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Additional phones in directory: 204-297-5883, 204-915-6397</t>
         </is>
@@ -5090,72 +5090,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Winnipeg (Charleswood)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>640 Pepperloaf Crescent, Winnipeg, MB R3R 1E8</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>204-837-9288</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>rpcc@wmba.ca</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>https://www.roblinpark.org/basketball</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Braden Cohoe (President)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>House-league/community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>https://www.roblinpark.org/basketball</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Type: community association (non-profit community centre, est. 1949, Charleswood). Basketball Convenor: Candace Perkins (rpcc@wmba.ca); Sports Director: Geoff Renouf; Board 2024-25 President Braden Cohoe, VP Heather Kovacs, Treasurer Wayne Tichon. General email: roblinparkcommunitycentre@gmail.com. Basketball registration flows through WMBA community league (WMBA site = RAMP InterActive). Phone from Yellow Pages listing (not shown on club site): https://www.yellowpages.ca/bus/Manitoba/Charleswood/Roblin-Park-Community-Centre/2504416.html. Sources: https://www.roblinpark.org/basketball, https://www.roblinpark.org/board-of-directors, https://www.roblinpark.org/contact-us.</t>
         </is>
@@ -5172,52 +5172,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>204-299-7918</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>wgpsummitbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Tara Meneer — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Boys &amp; girls rep teams ages 12–16</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials); Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -5234,42 +5234,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Winnipeg (West — St. James)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>jbourcier28@gmail.com</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Boys rep team (2008 birth year); tryouts at Sturgeon Heights Community Centre</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Peg City Showcase; Sea Bears Youth League (SBYL) 3x3 Series</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/08/showtime-basketball-club-announces.html</t>
         </is>
@@ -5286,67 +5286,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Winnipeg (South)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>666 Silverstone Avenue, Winnipeg, MB R3T 2V9</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>(204) 269-1908</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>basketball@swcc1.ca</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Type: community association (two sites: Fort Richmond 666 Silverstone Ave R3T 2V9, ph 204-269-1908; Waverley Heights 1885 Chancellor Dr R3T 4C4, ph 204-269-7000). Basketball convenor listed as 'Carrissa' (first name only) basketball@swcc1.ca; general/bookings booking@swcc1.ca. Board of Directors table on swcc1.ca/about/ lists positions but NO names (blank in page HTML — verified via raw fetch). Plays in WMBA community league. Platform intel: registration via RAMP (rampregistrations.com link on basketball page). Sources: https://swcc1.ca/basketball/, https://swcc1.ca/contact-us/, https://swcc1.ca/about/.</t>
         </is>
@@ -5363,62 +5363,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Winnipeg (Richmond West / Waverley Heights)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Richmond site (204-269-1908) and Waverley site (204-269-7000)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>204-269-1908</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>booking@swcc1.ca</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>WMBA catchment basketball ages 7-17 (7-8 co-ed; 9-12 girls / 9-13 boys; 13-17 girls / 14-17 boys) across Richmond and Waverley sites</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>multi-sport community centre</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>RAMP (via WMBA)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>https://swcc1.ca/basketball/</t>
         </is>
@@ -5435,37 +5435,37 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Winnipeg (South)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>wpgwildcatsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Girls club teams ages 13-17</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>community club (girls-focused)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2023-12-14T00:00:00-06:00&amp;max-results=50</t>
         </is>
@@ -5482,62 +5482,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Winnipeg (city-wide)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>204-914-5663</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>info@triumph204.com</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>https://www.triumph204.com</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Buchiza Mkanda — club contact (PSO registry; underclassmen staff)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Competitive youth program est. 2017, ages 12–18; Triumph Prime travel/exposure program; Triumph 204 local league/tournament teams; spring-summer competitive schedule</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>private club/training organization</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Jotform (tryout registration)</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
@@ -5554,52 +5554,52 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Winnipeg (East)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>204-333-7005</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>unitebasketball22@gmail.com</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Jordan Lopez — club contact (PSO registry)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Boys &amp; girls rep teams ages 11–12 and 15–16</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/ClubDirectory</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>In PSO registry; not seen in Fall 2025 Showcase entrant list</t>
         </is>
@@ -5616,11 +5616,6 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Winnipeg</t>
@@ -5628,35 +5623,40 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>323 - 145 Pacific Avenue, Winnipeg, Manitoba</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>info@pegcityball.ca</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Boys club teams born 2008-2010 (2024-25 tryout announcement)</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?updated-max=2025-07-02T00:00:00-05:00&amp;max-results=50</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Distinct from Unite Basketball; only registration-form contact published | enriched 2026-07-18</t>
         </is>
@@ -5673,42 +5673,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Boys teams 2009–2011 births and 2011 girls team</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/09/schedules-announced-for-peg-city.html</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Four league teams = clearly active, but no web presence found; unrelated to US clubs of same name</t>
         </is>
@@ -5725,72 +5725,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Winnipeg (Northeast — Valley Gardens)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>218 Antrim Road, Winnipeg, MB R2K 3L2</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>204-668-6927</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>basketballvgcc@gmail.com</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>https://valleygardenscc.squarespace.com/basketball</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Nancy Krahn — President</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Squarespace (club website); WMBA league ops on RAMP</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>https://valleygardenscc.squarespace.com/basketball</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Type: community centre (serving since 1976). Email listed is the VG basketball convener inbox (from basketball page); convener seat itself is vacant/being recruited per who-we-are page. General Manager: Mandy Furney; VP Operations James Franz; VP Programming Geoff L'Heureux. Registration via WMBA Community Centre League (wmba.ca), ages 7-17. Sources: https://valleygardenscc.squarespace.com/basketball ; https://valleygardenscc.squarespace.com/who-we-are</t>
         </is>
@@ -5807,62 +5807,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>204-471-1111</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>hello@visioneliteacademy.org</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>https://visioneliteacademy.org/basketball</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Multi-city private academy (Calgary HQ; Winnipeg, Edmonton, Fraser Valley): Vision Academy ages 7-11, Premier League ages 12-17 (internal seasonal league), Vision Basketball Club ages 12-18 competitive; 10-week year-round sessions; pay-per-session options</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>Vision Premier League (internal)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>private academy (multi-city)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Registration via own website program search</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>https://visioneliteacademy.org/basketball</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>HQ: The VISION Sport Centre, 7475 Flint Road, Calgary AB; Winnipeg venue address not published</t>
         </is>
@@ -5879,47 +5879,47 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Winnipeg (West)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>bballwestside@gmail.com</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Clarence Vigilance, Coach</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Boys club teams born 2013-2014; tryouts at Sport Manitoba (145 Pacific Ave)</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?max-results=100</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -5936,67 +5936,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Winnipeg (Whyte Ridge / SW)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>170 Fleetwood Rd, Winnipeg (WMBA outdoor courts on site)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>204-487-3042</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Office@whyteridge.ca</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>https://whyteridge.ca/sports/basketball/</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>House-league basketball via WMBA catchment: ages 7-8 co-ed 3v3, 9-12 (+13 boys), 14-17 (+13 girls) 5v5; fees WMBA $179 + CC $80 + $9 Canada Basketball</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>multi-sport community centre</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>RAMP (via WMBA central registration)</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>https://whyteridge.ca/sports/basketball/</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -6013,72 +6013,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Winnipeg (Southwest)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>170 Fleetwood Rd, Winnipeg, MB R3Y 1R3</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>204-487-3042</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Office@whyteridge.ca</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>https://whyteridge.ca/sports/basketball/</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Kirill Pirgalin — Board President (president@whyteridge.ca)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>WMBA community basketball for catchment area</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>https://whyteridge.ca/sports/basketball/</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Type: community centre (WMBA Community Centre League catchment; registration via wmba.ca). Basketball Director position VACANT — program email Basketball@whyteridge.ca. General Manager: Tenille Wilson (GeneralManager@whyteridge.ca). Sources: https://whyteridge.ca/contact/ ; https://whyteridge.ca/board/</t>
         </is>
@@ -6095,72 +6095,72 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Winnipeg (Windsor Park)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>980 Winakwa Road, Winnipeg, MB R2J 1E7</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>204-253-4418</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>valeriew@winakwacc.ca</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>https://winakwacc.ca/basketball</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Crystal Poirier — President (president@winakwacc.ca)</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Community basketball; fields catchment teams in WMBA leagues</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>multi-sport community centre (nonprofit)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>WMBA league operations on RAMP InterActive</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>https://winakwacc.ca/basketball</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Type: community centre. Email listed is Office Manager Valerie Wall (general contact); Building &amp; Grounds Manager Noel Beckel (noelb@winakwacc.ca). Basketball administered through WMBA (wmba.ca) — no club-side convenor listed. Sources: https://winakwacc.ca/contact-us ; https://winakwacc.ca/basketball</t>
         </is>
@@ -6177,67 +6177,67 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Winnipeg (East — East Elmwood)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>Bronx Park Community Centre, 720 Henderson Hwy (home facility)</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>winnipegblizzards@gmail.com</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>https://www.winnipegblizzardsbasketball.ca</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Ruel Maranan — lead founder (founded 2010 with Victor Santyo, John Aaron, Al Sansano, Ronald Millan, Treavor Stevenson, Jun Tabing, Gil Salunga, Richard Tamundong, Sony Valera, Mando De Leon, Ben San Jose)</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Non-profit volunteer-run club, boys ages 11–17 plus first girls team; low-cost model rooted in Filipino community</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>Manitoba Basketball Club Championships (provincials); PBA Winnipeg (Philippine Basketball Association of Winnipeg) — Youth Divisions; Peg City Club Basketball League (CBL); Sabado League; Attack Basketball community league</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>TeamSnap (scheduling/communication); Google Forms tryout registration</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>https://www.winnipegblizzardsbasketball.ca/p/about.html</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Type: community/volunteer non-profit club ('non-profitable basketball club aim to grow the sports thru volunteerism'). Email + leadership from club site (Blogspot-hosted): about page http://winnipegblizzardsbasketball.blogspot.com/p/about.html, contact page http://winnipegblizzardsbasketball.blogspot.com/p/contact.html. Competitive intel: uses TeamSnap for schedules/parent communication; Google Forms for tryout registration. Other named coaches: Vince Pinpin (16U boys head coach), Fred Mighty. | Also listed as: Winnipeg Blizzards Basketball</t>
         </is>
@@ -6254,57 +6254,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>chaoswinnipeg@gmail.com</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>https://chaosbasketball.ca/</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Chris Anderson — PSO directory contact; Grant Richter — Head Coach (also Executive Director of WMBA)</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Girls competitive club teams (15U-17U, born 2009-2012); summer/winter skills clinics boys 7-11 and girls 6-18; own outdoor practice courts; travels to national tournaments (BBall Nationals 2025)</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>community club (girls-focused)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Registration via own website</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>https://chaosbasketball.ca/</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Also listed as: Winnipeg Chaos</t>
         </is>
@@ -6321,42 +6321,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Winnipeg (West — St. James)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>jq14@shaw.ca</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Boys rep team (2010 birth year); tryouts at Sturgeon Heights Community Centre (210 Rita St.)</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/08/winnipeg-cobras-basketball-club-hosting.html</t>
         </is>
@@ -6373,62 +6373,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Winnipeg (Downtown)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Duckworth Centre, University of Winnipeg, Winnipeg, MB</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>al.cox@uwinnipeg.ca</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>https://wesmen.ca/sports/2024/6/25/winnipeg-junior-wesmen.aspx</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>University of Winnipeg Wesmen coaching staff (program oversight)</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Girls 15U (2010+) and 17U (2008–09) teams; trains 3x/week at Duckworth Centre Sept–May; fall league play + spring travel</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Peg City Showcase; Prairie Elite Basketball League (PEBL)</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>university-affiliated club program</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>https://wesmen.ca/sports/2024/6/25/winnipeg-junior-wesmen.aspx</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Type: university-run youth program (girls basketball, fall/winter/spring phases). Coordinator Alyssa Cox + email from program page — https://wesmen.ca/sports/2024/6/25/winnipeg-junior-wesmen.aspx. Practices at UWinnipeg Duckworth Centre, 400 Spence Street (facility phone 204-786-9349 — facility line, not program-specific; https://www.uwinnipeg.ca/recreation-services/facilities/duckworth-centre.html). Competitive intel: registration via Blackbaud registration forms (host.nxt.blackbaud.com), not RAMP/TeamLinkt.</t>
         </is>
@@ -6445,62 +6445,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Winnipeg (Downtown/Spence)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Duckworth Centre, 400 Spence St, Winnipeg</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>jrwesmen@gmail.com</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>https://wesmen.ca/sports/2024/6/25/winnipeg-junior-wesmen.aspx</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Overseen by UWinnipeg Wesmen coaching staff; contact Al Cox (al.cox@uwinnipeg.ca)</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Girls club programming (15U born 2010+, 17U born 2008-09), camps, seasonal training groups, facilitated by Wesmen student-athletes</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Prairie Elite Basketball League (PEBL)</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>university-affiliated youth program (girls)</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>https://wesmen.ca/sports/2024/6/25/winnipeg-junior-wesmen.aspx</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>PEBL is a league NOT in the pre-mapped Manitoba list — add to league map</t>
         </is>
@@ -6517,11 +6517,6 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Winnipeg</t>
@@ -6529,55 +6524,60 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>145 Pacific Ave, Winnipeg, MB R3B 2Z6</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>204-925-5774</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>info@wmba.ca</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Grant Richter — Executive Director; founded 1997 by Mike Ruta, Adam Wedlake, Dale Gamey, Jan Voss, Lori Hiscock, Larry Kabez</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>LEAGUE OPERATOR (not a club): Fall/Winter Community Centre League ages 7-17, Spring Community League, ELEVATE x WMBA 3x3 Summer League, Winter/Spring Skills Development, HoopFest; 200-400+ teams from community-centre catchments; fees ~$162-179 + CC fee + $9 Canada Basketball</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>WMBA Fall/Winter Community Centre League; WMBA Spring Community League; WMBA x ELEVATE 3x3 Youth Summer League</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>community nonprofit league operator</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registrations at rampregistrations.com/winnipegminorbasketball, official assigning, team app)</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>https://www.wmba.ca/</t>
         </is>
@@ -6594,37 +6594,37 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>wpgsaints@gmail.com</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Boys club team born 2010; tryouts at Valour Community Centre (715 Telfer St N)</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/search/label/Club%20Tryouts?max-results=100</t>
         </is>
@@ -6641,62 +6641,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Winnipeg (Northeast)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>207-525 Peguis St., Winnipeg, MB R3W 0G7</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>204-295-2006</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>alexbarra05@hotmail.com</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>https://www.winnipegteammayhem.com</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Alex Barra — Director of Operations (founder, running club 10+ years)</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Non-profit boys &amp; girls rep teams by grade; camps incl. Christmas break camp</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>Peg City Showcase; Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>https://www.winnipegteammayhem.com/en/</t>
         </is>
@@ -6713,57 +6713,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Winnipeg (St. Boniface)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>winnipegwolves@gmail.com</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>http://www.winnipegwolves.com</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Martin Riley — founder (Canada Basketball Hall of Fame member); mjriley14@gmail.com</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Operating since 2006; recent seasons girls U15/U18 teams; training programs; tryouts at Université de Saint-Boniface</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>Blogger (website)</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>http://www.winnipegwolves.com/</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Not in Fall 2025 Showcase entrant list — current activity level uncertain</t>
         </is>
@@ -6780,42 +6780,42 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Winnipeg</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Boys team (2010 birth year)</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>Peg City Showcase</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>community club (unverified structure)</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/09/schedules-announced-for-peg-city.html</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Type: rep/club program. Only verifiable footprint: team 'Wolf Pack 2010 Boys' in Peg City Showcase Basketball League Fall 2025 (source: https://www.basketballmanitoba.ca/2025/09/schedules-announced-for-peg-city.html). NOT in Basketball Manitoba club directory. No club website/registry entry found. Disambiguation (do not conflate): wolfpack-basketball.com = Whitehorse, Yukon club; wolfpackbasketball.ca = Chestermere AB club (site now dead, archived 2019); winnipegwolfpack.com + @winnipegwolfpack socials = women's tackle football, not basketball; wolfpackbasketball.org = US org. Platform intel: Peg City league runs on RAMP InterActive.</t>
         </is>
@@ -6832,63 +6832,63 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="inlineStr">
         <is>
           <t>Winnipeg (South — Linden Woods)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>worldclasshoopers@gmail.com</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>https://www.instagram.com/worldclasshoopers/</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Steven Wesley — Founder</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Boys born 2008–2015 and girls born 2008–2012; multiple teams per age (Rise/Surge); 'The Hooper Lab' 8-week winter training; summer clinic; tryouts at Linden Woods CC</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Peg City Showcase; Manitoba Basketball Club Championships (provincials); Peg City Club Basketball League (CBL)</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>community club (nonprofit status unverified)</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>https://www.basketballmanitoba.ca/2025/07/world-class-hoopers-announces-202526.html</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>Type: private club/academy program. Founder Steven Wesley confirmed via Winnipeg Sea Bears 2026 coaching staff announcement ('He is also the founder of World Class Hoopers') — https://www.seabears.ca/winnipeg-sea-bears-announce-2026-coaching-staff. Email from Basketball Manitoba tryout announcement — https://www.basketballmanitoba.ca/2025/07/world-class-hoopers-announces-202526.html. No standalone website found; Instagram is primary presence. Registration via Google Forms (no commercial platform). Tryouts at Linden Woods Community Centre; 'Hooper Lab' winter training in South/Southwest/West Winnipeg (https://www.basketballmanitoba.ca/2026/01/world-class-hoopers-launches-hooper-lab.html). Teams compete in Peg City league (RAMP-hosted league pages, e.g. https://pegcityball.club/team/10819/3420/30195/264989).</t>
         </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -6902,57 +6902,57 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Winnipeg (Downtown)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>333 King Street, Winnipeg, MB R3B 0N1</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>204-669-4205</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Jamie.wilson@yfcwinnipeg.ca</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>https://yfc.ca/winnipeg/program/club-basketball/</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Jamie Wilson — program contact; YFC Winnipeg is a registered charity (#119307619 RR0001)</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Free boys club basketball ages 13-17 (grades 8-12), Thursdays Sep-Dec: skills, scrimmages, faith-based mentorship; first-year program forming new teams weekly</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>multi-sport/faith-based charity youth org</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>https://yfc.ca/winnipeg/program/club-basketball/</t>
         </is>
@@ -6969,62 +6969,62 @@
           <t>Manitoba</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Winnipeg (Downtown)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Winnipeg</t>
-        </is>
-      </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t>333 King Street, Winnipeg, MB R3B 0N1</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>(204) 669-4205</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>Jamie.wilson@yfcwinnipeg.ca</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>https://yfc.ca/winnipeg/program/club-basketball/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Jamie Wilson — program contact</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Free weekly boys basketball (ages 13–17, Grades 8–12), Thursdays Sept–Dec; skills + scrimmages; facility also hosts club tryouts (e.g., Empire)</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>faith-based charity / multi-sport youth org (registered charity #119307619 RR0001)</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>https://yfc.ca/winnipeg/program/club-basketball/</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Drop-in development program, not a rep club</t>
         </is>
